--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488216_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488216_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7763</v>
+        <v>7.4055</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4418</v>
+        <v>8.095599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6655</v>
+        <v>-0.6902</v>
       </c>
       <c r="G2" t="n">
         <v>6.9269</v>
@@ -610,13 +610,13 @@
         <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1893</v>
+        <v>0.4399</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3407</v>
+        <v>0.3131</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1514</v>
+        <v>0.1268</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2583</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2046</v>
+        <v>4.6105</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0683</v>
+        <v>6.3511</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8637</v>
+        <v>-1.7406</v>
       </c>
       <c r="G3" t="n">
         <v>6.5745</v>
@@ -688,13 +688,13 @@
         <v>2.7793</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3331</v>
+        <v>0.739</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3443</v>
+        <v>0.6271</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0112</v>
+        <v>0.1119</v>
       </c>
       <c r="V3" t="n">
         <v>-2.5177</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8358</v>
+        <v>1.9391</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8068</v>
+        <v>1.3286</v>
       </c>
       <c r="F4" t="n">
-        <v>1.029</v>
+        <v>0.6105</v>
       </c>
       <c r="G4" t="n">
         <v>3.6271</v>
@@ -766,13 +766,13 @@
         <v>2.2234</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8387</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.725</v>
+        <v>0.2469</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1137</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-1.8888</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3767</v>
+        <v>0.9702</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4147</v>
+        <v>1.4584</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.038</v>
+        <v>-0.4882</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9126</v>
+        <v>-1.2495</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7299</v>
+        <v>-1.7381</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1827</v>
+        <v>0.4886</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1384</v>
+        <v>0.8356</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2628</v>
+        <v>-0.1597</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1244</v>
+        <v>0.9953</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7743</v>
+        <v>-2.0851</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4671</v>
+        <v>-1.5784</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3071</v>
+        <v>-0.5067</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1853</v>
+        <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8452</v>
+        <v>0.8496</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9797</v>
+        <v>0.7912</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1346</v>
+        <v>0.0584</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2589</v>
+        <v>0.6289</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5733</v>
+        <v>0.9433</v>
       </c>
       <c r="X6" t="n">
         <v>-0.3144</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3591</v>
+        <v>0.3295</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9458</v>
+        <v>1.3921</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5867</v>
+        <v>-1.0626</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2495</v>
+        <v>-1.9126</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7381</v>
+        <v>-1.7299</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4886</v>
+        <v>-0.1827</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8356</v>
+        <v>-1.1384</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1597</v>
+        <v>-1.2628</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9953</v>
+        <v>0.1244</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0851</v>
+        <v>-0.7743</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5784</v>
+        <v>-0.4671</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5067</v>
+        <v>-0.3071</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8529</v>
+        <v>0.1853</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2385</v>
+        <v>0.798</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2786</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0401</v>
+        <v>-0.1592</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6289</v>
+        <v>1.2589</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9433</v>
+        <v>1.5733</v>
       </c>
       <c r="X8" t="n">
         <v>-0.3144</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9993</v>
+        <v>-0.0214</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1803</v>
+        <v>-0.4155</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1796</v>
+        <v>0.3941</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7163</v>
+        <v>-0.632</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3615</v>
+        <v>-1.1757</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3548</v>
+        <v>0.5436</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1044</v>
+        <v>0.9221</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0215</v>
+        <v>0.7857</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0829</v>
+        <v>0.1363</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8207</v>
+        <v>-1.5541</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.383</v>
+        <v>-1.9614</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4377</v>
+        <v>0.4073</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7793</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.283</v>
+        <v>0.499</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0759</v>
+        <v>0.0712</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3589</v>
+        <v>0.4278</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.002</v>
+        <v>-0.6995</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3147</v>
+        <v>0.4308</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3127</v>
+        <v>-1.1303</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4397</v>
+        <v>-0.7163</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2217</v>
+        <v>-0.3615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.218</v>
+        <v>-0.3548</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8264</v>
+        <v>0.1044</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8465</v>
+        <v>0.0215</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0201</v>
+        <v>0.0829</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3867</v>
+        <v>-0.8207</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6248</v>
+        <v>-0.383</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2381</v>
+        <v>-0.4377</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.9646</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5228</v>
+        <v>0.0168</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5646</v>
+        <v>0.3264</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9583</v>
+        <v>-0.3096</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1911</v>
+        <v>-1.3659</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2651</v>
+        <v>-1.26</v>
       </c>
       <c r="F11" t="n">
-        <v>0.074</v>
+        <v>-0.1059</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.632</v>
+        <v>0.4397</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1757</v>
+        <v>0.2217</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5436</v>
+        <v>0.218</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9221</v>
+        <v>1.8264</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7857</v>
+        <v>1.8465</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1363</v>
+        <v>-0.0201</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5541</v>
+        <v>-1.3867</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9614</v>
+        <v>-1.6248</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4073</v>
+        <v>0.2381</v>
       </c>
       <c r="P11" t="n">
+        <v>-2.9646</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-3.7057</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.7411</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-2.0382</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.7793</v>
-      </c>
       <c r="S11" t="n">
-        <v>-0.6708</v>
+        <v>1.159</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7784</v>
+        <v>0.6193</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1077</v>
+        <v>0.5397</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8556</v>
+        <v>-2.1384</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6077</v>
+        <v>-0.1612</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.248</v>
+        <v>-1.9771</v>
       </c>
       <c r="G12" t="n">
         <v>0.3827</v>
@@ -1390,13 +1390,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6824</v>
+        <v>0.0348</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3407</v>
+        <v>0.1057</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3417</v>
+        <v>-0.0709</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2589</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3833</v>
+        <v>-3.8143</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3036</v>
+        <v>-3.7593</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0551</v>
       </c>
       <c r="G13" t="n">
         <v>-5.0622</v>
@@ -1468,13 +1468,13 @@
         <v>1.297</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3206</v>
+        <v>0.2484</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4924</v>
+        <v>0.0519</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1718</v>
+        <v>0.1965</v>
       </c>
       <c r="V13" t="n">
         <v>0.6289</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.3316</v>
+        <v>9.425699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>14.577</v>
+        <v>15.671</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.245500000000001</v>
+        <v>-6.245400000000001</v>
       </c>
       <c r="G14" t="n">
         <v>10.5887</v>
@@ -1519,7 +1519,7 @@
         <v>10.0228</v>
       </c>
       <c r="J14" t="n">
-        <v>23.5361</v>
+        <v>23.53609999999999</v>
       </c>
       <c r="K14" t="n">
         <v>13.3611</v>
@@ -1546,13 +1546,13 @@
         <v>13.8965</v>
       </c>
       <c r="S14" t="n">
-        <v>4.6322</v>
+        <v>5.7265</v>
       </c>
       <c r="T14" t="n">
-        <v>3.0159</v>
+        <v>4.109999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6164</v>
+        <v>1.6165</v>
       </c>
       <c r="V14" t="n">
         <v>-5.0364</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1251</v>
+        <v>2.5254</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5872</v>
+        <v>2.7831</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4621</v>
+        <v>-0.2577</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1543</v>
@@ -1624,13 +1624,13 @@
         <v>0.9264</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8225</v>
+        <v>-0.4222</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4924</v>
+        <v>-0.2966</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.33</v>
+        <v>-0.1256</v>
       </c>
       <c r="V15" t="n">
         <v>4.0283</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. LEÓN TEJERA</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6221</v>
+        <v>0.9421</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6221</v>
+        <v>1.4138</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.4717</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6221</v>
+        <v>0.3986</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.3969</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6221</v>
+        <v>0.0016</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6221</v>
+        <v>1.863</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.1165</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6221</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-1.4644</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.7196</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.7448</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.5611</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.4492</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.1119</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3777</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.3777</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>B. LEÓN TEJERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.6221</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3158</v>
+        <v>0.6221</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7821</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3986</v>
+        <v>0.6221</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3969</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0016</v>
+        <v>0.6221</v>
       </c>
       <c r="J17" t="n">
-        <v>1.863</v>
+        <v>0.6221</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1165</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.6221</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4644</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7196</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7448</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9695</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5471</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4223</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3777</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. GALIANO AVILA</t>
+          <t>M. CASERO MIGLIAVACCA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3637</v>
+        <v>0.5606</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0061</v>
+        <v>2.4979</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6424</v>
+        <v>-1.9373</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9905</v>
+        <v>-0.514</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0227</v>
+        <v>0.7457</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9678</v>
+        <v>-1.2597</v>
       </c>
       <c r="J18" t="n">
-        <v>2.568</v>
+        <v>3.2654</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1165</v>
+        <v>3.212</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4515</v>
+        <v>0.0534</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5775</v>
+        <v>-3.7794</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0938</v>
+        <v>-2.4663</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4837</v>
+        <v>-1.3131</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3706</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R18" t="n">
-        <v>1.297</v>
+        <v>2.2234</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6835</v>
+        <v>-0.1946</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6354</v>
+        <v>-0.1909</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.048</v>
+        <v>-0.0037</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3139</v>
+        <v>1.8251</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3139</v>
+        <v>-0.3777</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CASERO MIGLIAVACCA</t>
+          <t>S. GALIANO AVILA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4605</v>
+        <v>0.5258</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9103</v>
+        <v>1.1041</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3708</v>
+        <v>-0.5783</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.514</v>
+        <v>0.9905</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7457</v>
+        <v>0.0227</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2597</v>
+        <v>0.9678</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2654</v>
+        <v>2.568</v>
       </c>
       <c r="K19" t="n">
-        <v>3.212</v>
+        <v>1.1165</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0534</v>
+        <v>1.4515</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.7794</v>
+        <v>-1.5775</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.4663</v>
+        <v>-1.0938</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3131</v>
+        <v>-0.4837</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2234</v>
+        <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2157</v>
+        <v>-0.5214</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7784</v>
+        <v>-0.5375</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4372</v>
+        <v>0.0161</v>
       </c>
       <c r="V19" t="n">
-        <v>1.8251</v>
+        <v>-0.3139</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3777</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5987</v>
+        <v>-1.007</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1083</v>
+        <v>-1.027</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1786</v>
@@ -2014,13 +2014,13 @@
         <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.3634</v>
       </c>
       <c r="T20" t="n">
-        <v>0.868</v>
+        <v>0.3784</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0963</v>
+        <v>-0.0149</v>
       </c>
       <c r="V20" t="n">
         <v>0.2523</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. PERRY II</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5364</v>
+        <v>-1.5368</v>
       </c>
       <c r="E21" t="n">
-        <v>1.161</v>
+        <v>-0.8193</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6974</v>
+        <v>-0.7174</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.148</v>
+        <v>-3.6111</v>
       </c>
       <c r="H21" t="n">
-        <v>2.6247</v>
+        <v>-2.7048</v>
       </c>
       <c r="I21" t="n">
-        <v>-5.7727</v>
+        <v>-0.9062</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0227</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7834</v>
+        <v>-0.7522</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.7607</v>
+        <v>0.1458</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.1707</v>
+        <v>-3.0047</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.1587</v>
+        <v>-1.9527</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.012</v>
+        <v>-1.052</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7411</v>
+        <v>2.594</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>2.594</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3885</v>
+        <v>-0.1421</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4179</v>
+        <v>-0.2129</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8063</v>
+        <v>0.0709</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2589</v>
+        <v>-0.3777</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3144</v>
+        <v>-0.3777</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6989</v>
+        <v>-1.5794</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9173</v>
+        <v>1.0203</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7816</v>
+        <v>-2.5997</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.6111</v>
+        <v>0.1301</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7048</v>
+        <v>-1.0294</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9062</v>
+        <v>1.1596</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6064000000000001</v>
+        <v>3.5265</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7522</v>
+        <v>0.9233</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1458</v>
+        <v>2.6033</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.0047</v>
+        <v>-3.3964</v>
       </c>
       <c r="N22" t="n">
         <v>-1.9527</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.052</v>
+        <v>-1.4437</v>
       </c>
       <c r="P22" t="n">
-        <v>2.594</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R22" t="n">
-        <v>2.594</v>
+        <v>2.2234</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3042</v>
+        <v>-0.2273</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3109</v>
+        <v>-0.0594</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0067</v>
+        <v>-0.1679</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3777</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3777</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>T. PERRY II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8165</v>
+        <v>-1.6911</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1182</v>
+        <v>0.6713</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9347</v>
+        <v>-2.3624</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1301</v>
+        <v>-3.148</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0294</v>
+        <v>2.6247</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1596</v>
+        <v>-5.7727</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5265</v>
+        <v>1.0227</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9233</v>
+        <v>4.7834</v>
       </c>
       <c r="L23" t="n">
-        <v>2.6033</v>
+        <v>-3.7607</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.3964</v>
+        <v>-4.1707</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9527</v>
+        <v>-2.1587</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4437</v>
+        <v>-2.012</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.4823</v>
+        <v>0.7411</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.7057</v>
+        <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2234</v>
+        <v>2.594</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4643</v>
+        <v>-0.5431</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0386</v>
+        <v>-0.0718</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5029</v>
+        <v>-0.4713</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2589</v>
+        <v>1.5733</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.865</v>
+        <v>-5.7344</v>
       </c>
       <c r="E24" t="n">
         <v>-3.0677</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7973</v>
+        <v>-2.6667</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1238</v>
@@ -2326,13 +2326,13 @@
         <v>0.9264</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.4253</v>
       </c>
       <c r="T24" t="n">
         <v>-0.1766</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3793</v>
+        <v>-0.2487</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2589</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.331300000000001</v>
+        <v>-6.3727</v>
       </c>
       <c r="E25" t="n">
-        <v>6.2453</v>
+        <v>6.2456</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.5767</v>
+        <v>-12.6182</v>
       </c>
       <c r="G25" t="n">
         <v>-10.5885</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5656000000000003</v>
+        <v>-0.5656000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-10.0228</v>
@@ -2383,7 +2383,7 @@
         <v>12.7956</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1520999999999999</v>
+        <v>0.1521000000000003</v>
       </c>
       <c r="M25" t="n">
         <v>-23.5361</v>
@@ -2404,13 +2404,13 @@
         <v>15.7492</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.632400000000001</v>
+        <v>-2.6737</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.6163</v>
+        <v>-1.6165</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.0156</v>
+        <v>-1.057</v>
       </c>
       <c r="V25" t="n">
         <v>5.0364</v>
